--- a/authorization_forms/005_sticker_usage_agreement_form--authorization_forms.xlsx
+++ b/authorization_forms/005_sticker_usage_agreement_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sticker_usage_agreement_form_first_page</t>
+          <t>user_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sticker_usage_agreement_form_first_page</t>
+          <t>User Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sticker_usage_agreement_form_second_page</t>
+          <t>usage_details</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sticker_usage_agreement_form_second_page</t>
+          <t>Usage Details</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sticker_placement_request_details</t>
+          <t>sticker_placement_request</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sticker_placement_request_details</t>
+          <t>Sticker Placement Request</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sticker_placement_request_location</t>
+          <t>approval_request</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sticker_placement_request_location</t>
+          <t>Approval Request</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval</t>
+          <t>approval_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval</t>
+          <t>Approval Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,20 +630,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval_status</t>
+          <t>renewal_request</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval_status</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Renewal Request</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>When is the sticker expected to be renewed?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_reason</t>
+          <t>renewal_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_reason</t>
+          <t>Renewal Status</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +680,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_date</t>
+          <t>renewal_notes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_date</t>
+          <t>Renewal Notes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +703,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_by</t>
+          <t>renewal_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_by</t>
+          <t>Renewal Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +731,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_reason</t>
+          <t>reason_for_renewal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sticker_placement_request_rejected_reason</t>
+          <t>Reason for Renewal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,20 +749,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_date</t>
+          <t>renewal_condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Renewal Condition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What are the conditions for sticker renewal?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status</t>
+          <t>sticker_status</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status</t>
+          <t>Sticker Status</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +804,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_date</t>
+          <t>expiration_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_date</t>
+          <t>Expiration Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +822,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status</t>
+          <t>approval_date</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status</t>
+          <t>Approval Date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +850,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_notes</t>
+          <t>approval_by</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_notes</t>
+          <t>Approval By</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,20 +868,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_date</t>
+          <t>approval_condition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Approval Condition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>What are the conditions for sticker approval?</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +895,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status</t>
+          <t>usage_condition</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Usage Condition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>What are the conditions for sticker usage?</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,177 +927,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_notes</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_notes</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Any additional notes?</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_notes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_notes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_notes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +957,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +985,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sticker_placement_request_details_choices</t>
+          <t>sticker_placement_request_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1002,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sticker_placement_request_details_choices</t>
+          <t>sticker_placement_request_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1019,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval_choices</t>
+          <t>approval_request_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1036,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval_choices</t>
+          <t>approval_request_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1053,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval_status_choices</t>
+          <t>approval_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1070,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sticker_placement_request_approval_status_choices</t>
+          <t>approval_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1087,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
+          <t>renewal_status_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1104,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
+          <t>renewal_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1121,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
+          <t>sticker_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1138,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
+          <t>sticker_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1288,108 +1147,6 @@
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>sticker_placement_request_renewal_status_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
